--- a/output/full_scan/batch_seq8_2026-06-05.xlsx
+++ b/output/full_scan/batch_seq8_2026-06-05.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1014.013152415968</v>
+        <v>1289.013152415968</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>224</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>68.74756028964046</v>
+        <v>68.74755824247401</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>30.78220738832755</v>
+        <v>30.78220735930786</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.401315241596843</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.187011457734942</v>
+        <v>1.187011487212692</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6907</v>
+        <v>6895</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>867.9714453781263</v>
+        <v>1130</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>169</v>
+        <v>169.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>76.21480711442634</v>
+        <v>61.51668190846567</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>27.57181538386602</v>
+        <v>16.18379620169262</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.297144537812629</v>
+        <v>5.269444288678293</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>4.807512216452084</v>
+        <v>1.551217767110035</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6895</v>
+        <v>6907</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>855</v>
+        <v>1067.971445378126</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>169.5</v>
+        <v>169</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>61.51668189458356</v>
+        <v>76.21480711442634</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>16.18379620180819</v>
+        <v>27.57181538386602</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.269444288678293</v>
+        <v>4.297144537812629</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.55121776674755</v>
+        <v>4.807512216452084</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7791</v>
+        <v>6890</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>840.6380904836608</v>
+        <v>1035</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>69.2</v>
+        <v>242.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>73.02730245383505</v>
+        <v>87.27198783050402</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>30.62538851466434</v>
+        <v>31.37334634391264</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3.063809048366076</v>
+        <v>6.270477745240651</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.5061356034514619</v>
+        <v>8.021716617986367</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8040</v>
+        <v>7791</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>754.1315680010264</v>
+        <v>955.6380904836608</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>102.5</v>
+        <v>69.2</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.23457697718582</v>
+        <v>73.02730253893429</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>48.42487078185607</v>
+        <v>30.6253885195234</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.4131568001026345</v>
+        <v>3.063809048366076</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,11 +782,11 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-2.030483240885065</v>
+        <v>0.506135603356053</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>739.4028862152188</v>
+        <v>939.4028862152188</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>390</v>
@@ -817,7 +817,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>66.36630475254935</v>
+        <v>66.36630484086595</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>23.90047301234215</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>8.220557932287317</v>
+        <v>8.220557929997744</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6916</v>
+        <v>6936</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>699.5998095620604</v>
+        <v>916.4430099496282</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20.45</v>
+        <v>34.55</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>70.27806006936592</v>
+        <v>61.2536885496198</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.33535846706538</v>
+        <v>15.07931623296681</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>3.959980956206042</v>
+        <v>2.644300994962815</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.2556915507857145</v>
+        <v>0.15991122069958</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7714</v>
+        <v>8028</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>696.6258734206717</v>
+        <v>909.771138647022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>140</v>
+        <v>337.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>67.69927455871768</v>
+        <v>66.5226962974491</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>22.96916806587972</v>
+        <v>50.03306794457021</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>4.162587342067167</v>
+        <v>0.4771138647021996</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.767841730407954</v>
+        <v>2.39457850332257</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6936</v>
+        <v>6916</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>686.4430099496282</v>
+        <v>899.5998095620604</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>34.55</v>
+        <v>20.45</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.25368851562588</v>
+        <v>70.27806017483408</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.0793159645233</v>
+        <v>22.33535842496646</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.644300994962815</v>
+        <v>3.959980956206042</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1599112207472779</v>
+        <v>0.2556915508429536</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8042</v>
+        <v>7714</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>677.8479472730347</v>
+        <v>896.6258734206717</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>145.5</v>
+        <v>140</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>65.48457999657869</v>
+        <v>67.69927463991672</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>47.85998481069804</v>
+        <v>22.96916807118589</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.7847947273034727</v>
+        <v>4.162587342067167</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,11 +1047,11 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.008744755148200001</v>
+        <v>1.767841730694142</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>677.3190523315266</v>
+        <v>862.3190523315266</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>303.5</v>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>67.5092046210811</v>
+        <v>67.50920460608997</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>66.55952185683134</v>
+        <v>66.55952185291295</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>0.7319052331526604</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-1.365650620879769</v>
+        <v>-1.365650619448797</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8028</v>
+        <v>6925</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>674.771138647022</v>
+        <v>861.1278065056495</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>337.5</v>
+        <v>76.2</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>66.52269628433386</v>
+        <v>69.55363330522675</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>50.0330680409772</v>
+        <v>30.26473541741047</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4771138647021996</v>
+        <v>2.612780650564942</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2.39457850332257</v>
+        <v>2.190878561739572</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6902</v>
+        <v>7772</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>673.4318020180976</v>
+        <v>843.4388451634284</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>143</v>
+        <v>184.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>67.12796816022227</v>
+        <v>56.65596594877927</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>49.06252438673422</v>
+        <v>13.41900991510623</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.343180201809768</v>
+        <v>2.343884516342835</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.3467775540088311</v>
+        <v>1.349020936326522</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7721</v>
+        <v>8043</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>672.2612055225698</v>
+        <v>843.3186297895548</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>78.3</v>
+        <v>159.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>53.51360044139875</v>
+        <v>71.03825086695063</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>14.66025476490561</v>
+        <v>40.98376982678895</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.226120552256972</v>
+        <v>1.331862978955489</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0287990215086819</v>
+        <v>2.270995575314538</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6890</v>
+        <v>7610</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>665</v>
+        <v>842.8929307190896</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>242.5</v>
+        <v>1750</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>87.27198765974349</v>
+        <v>89.88310895193815</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>31.37334637317817</v>
+        <v>74.64007691777849</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>6.270477745240651</v>
+        <v>0.2892930719089598</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>8.02171661970355</v>
+        <v>41.88671912173498</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7556</v>
+        <v>7721</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>664.8986255424029</v>
+        <v>842.2612055225698</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>281.5</v>
+        <v>78.3</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.36071807688941</v>
+        <v>53.51360044483504</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.0587688016401</v>
+        <v>14.66025477201475</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4898625542402853</v>
+        <v>1.226120552256972</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,11 +1365,11 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-1.444379346951254</v>
+        <v>0.0287990215277615</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>664.1827518217622</v>
+        <v>834.1827518217622</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>285.5</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>67.39420858132581</v>
+        <v>67.39420858855362</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>35.90998651086203</v>
+        <v>35.90998652527896</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1.418275182176211</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>5.894484678166354</v>
+        <v>5.894484679597284</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6925</v>
+        <v>6859</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>661.1278065056495</v>
+        <v>813.8895929767867</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>76.2</v>
+        <v>132</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>69.55363325184256</v>
+        <v>62.46126941967236</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>30.264735386268</v>
+        <v>23.98916997369329</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.612780650564942</v>
+        <v>0.3889592976786758</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>2.190878561644172</v>
+        <v>1.129978836240378</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6894</v>
+        <v>7827</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>660.9896872167728</v>
+        <v>807.3963139668534</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>384</v>
+        <v>159.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>57.11030800645192</v>
+        <v>62.51006248838168</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>34.96491149169212</v>
+        <v>22.1221221245295</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.598968721677286</v>
+        <v>1.239631396685346</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.542413817591008</v>
+        <v>2.955455471254337</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7711</v>
+        <v>6910</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>660.7816278128292</v>
+        <v>780.6324610731591</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>393</v>
+        <v>30</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>52.42461255921345</v>
+        <v>61.66753614735615</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>22.13468628342288</v>
+        <v>17.89849969611254</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.578162781282926</v>
+        <v>2.563246107315913</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-3.02926000710103</v>
+        <v>0.3250970119288975</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6862</v>
+        <v>7556</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>654.5630180064657</v>
+        <v>779.8986255424029</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>204.5</v>
+        <v>281.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.37116876515096</v>
+        <v>54.36071812082127</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20.01669258575179</v>
+        <v>22.05876879291866</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.9563018006465608</v>
+        <v>0.4898625542402853</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.748910517677634</v>
+        <v>-1.444379346951254</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7772</v>
+        <v>7765</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>643.4388451634284</v>
+        <v>776.6779550248046</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>184.5</v>
+        <v>259</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>56.65596594877927</v>
+        <v>59.77173197011842</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>13.41900991510623</v>
+        <v>39.72866742062619</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.343884516342835</v>
+        <v>0.6677955024804682</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.349020936326522</v>
+        <v>0.7662316953229595</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8043</v>
+        <v>8032</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>643.3186297895548</v>
+        <v>759.7224136665022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>159.5</v>
+        <v>45.25</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>71.03825086484861</v>
+        <v>59.23484494682032</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>40.98376987614101</v>
+        <v>36.239275830959</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.331862978955489</v>
+        <v>0.9722413666502204</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>2.270995575209618</v>
+        <v>0.0286701263766975</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7765</v>
+        <v>8044</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>636.6779550248046</v>
+        <v>755.2940229169992</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>259</v>
+        <v>29.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>59.77173175602646</v>
+        <v>63.36797039211505</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>39.72866749674434</v>
+        <v>40.60936622893669</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6677955024804682</v>
+        <v>0.5294022916999248</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.7662316976125103</v>
+        <v>0.2318975045105227</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6861</v>
+        <v>8040</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>620.198033696119</v>
+        <v>754.1315680010264</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>351.5</v>
+        <v>102.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46.19554138736441</v>
+        <v>57.23457697254754</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>46.19878851073462</v>
+        <v>48.42487086659882</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5198033696118906</v>
+        <v>0.4131568001026345</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-19.34540239859907</v>
+        <v>-2.030483240598869</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8032</v>
+        <v>6997</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>619.7224136665022</v>
+        <v>717.8629076434285</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>45.25</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.23484488867594</v>
+        <v>54.14657831037329</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>36.23927597374104</v>
+        <v>5.154051301848855</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9722413666502204</v>
+        <v>1.286290764342841</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0286701261668294</v>
+        <v>0.1633057427225082</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6899</v>
+        <v>7705</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>619.3705304522866</v>
+        <v>709.5755148247327</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>62.2</v>
+        <v>32.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>54.77676958945235</v>
+        <v>57.23979897063676</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30.58700950958193</v>
+        <v>27.78356062206568</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4370530452286675</v>
+        <v>0.957551482473276</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.3135571970471034</v>
+        <v>0.2799806480286634</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>7805</v>
+        <v>6899</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>616.606489372751</v>
+        <v>709.3705304522866</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>758</v>
+        <v>62.2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>53.93215476444111</v>
+        <v>54.77676958667123</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>37.14499969957611</v>
+        <v>30.58700953615286</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6606489372750988</v>
+        <v>0.4370530452286675</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-1.040484003896921</v>
+        <v>-0.313557196970788</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8044</v>
+        <v>7828</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>615.2940229169992</v>
+        <v>699.5669629573283</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>29.9</v>
+        <v>1565</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>63.36797032448241</v>
+        <v>61.83240033956551</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>40.60936612953715</v>
+        <v>17.15976740424421</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5294022916999248</v>
+        <v>0.4566962957328327</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.2318975045200606</v>
+        <v>37.83350352494011</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6910</v>
+        <v>7722</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>610.6324610731591</v>
+        <v>699.2588775641439</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>30</v>
+        <v>305.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>61.66753626970799</v>
+        <v>66.37571807380759</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>17.89849976330557</v>
+        <v>27.80502656640174</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.563246107315913</v>
+        <v>1.425887756414388</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.3250970116140895</v>
+        <v>5.894443357186828</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7712</v>
+        <v>6957</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>604.2321870731851</v>
+        <v>689.8156113150196</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>150</v>
+        <v>191.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>49.49276964323277</v>
+        <v>76.50662866380773</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>30.24475550363993</v>
+        <v>28.13489042806047</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4232187073185066</v>
+        <v>1.481561131501961</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-3.36429817530629</v>
+        <v>3.613579744132726</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7769</v>
+        <v>6885</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>602.3148150950365</v>
+        <v>689.3717723206662</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>7275</v>
+        <v>26.55</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>56.08133526778013</v>
+        <v>70.82462709260429</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>39.47539851402051</v>
+        <v>20.96675036478694</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7314815095036464</v>
+        <v>2.437177232066618</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-126.6454559377516</v>
+        <v>0.543861513349557</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6903</v>
+        <v>7712</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>600.7899839730266</v>
+        <v>679.2321870731851</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>393</v>
+        <v>150</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>49.03353206444906</v>
+        <v>49.4927697289256</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>25.09029127353419</v>
+        <v>30.24475550363993</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.578998397302659</v>
+        <v>0.4232187073185066</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-2.793184285650256</v>
+        <v>-3.3642981752109</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6922</v>
+        <v>8042</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>599.6386796249965</v>
+        <v>677.8479472730347</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>184.5</v>
+        <v>145.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>48.94346344794253</v>
+        <v>65.48457999920565</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>31.00432411886906</v>
+        <v>47.85998466146238</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.4638679624996468</v>
+        <v>0.7847947273034727</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-1.087150868351105</v>
+        <v>0.0087447552912891</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6951</v>
+        <v>6902</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>598.9473119451987</v>
+        <v>673.4318020180976</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>55.06304613435817</v>
+        <v>67.12796816022227</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>30.52573275587247</v>
+        <v>49.06252443528732</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.894731194519875</v>
+        <v>0.343180201809768</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.1023104289163622</v>
+        <v>0.3467775539134354</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6859</v>
+        <v>6894</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>583.8895929767867</v>
+        <v>660.9896872167728</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>132</v>
+        <v>384</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>62.46126919300133</v>
+        <v>57.11030807554656</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.98916989387568</v>
+        <v>34.96491150916834</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.3889592976786758</v>
+        <v>0.598968721677286</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.129978836908158</v>
+        <v>2.542413817209393</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6913</v>
+        <v>7711</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>583.1364884617898</v>
+        <v>660.7816278128292</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>134</v>
+        <v>393</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>48.32396970563991</v>
+        <v>52.42461260092709</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>20.85923471927459</v>
+        <v>22.13468643764634</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.313648846178974</v>
+        <v>1.578162781282926</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-1.118264701762185</v>
+        <v>-3.029260010058312</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7705</v>
+        <v>6862</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>569.5755148247327</v>
+        <v>654.5630180064657</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>32.5</v>
+        <v>204.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>57.23979862600772</v>
+        <v>57.37116878822114</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>27.78356006567252</v>
+        <v>20.01669255958882</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.957551482473276</v>
+        <v>0.9563018006465608</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.2799806481049817</v>
+        <v>1.748910517677634</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6906</v>
+        <v>6855</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>554.3620101785466</v>
+        <v>645.4171929384768</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>69.21375187585855</v>
+        <v>58.75665035985487</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>42.92703728853967</v>
+        <v>11.92375154732532</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4362010178546667</v>
+        <v>1.041719293847682</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.399985229001633</v>
+        <v>2.229757948185351</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7610</v>
+        <v>6906</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>552.8929307190896</v>
+        <v>644.3620101785467</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1750</v>
+        <v>101</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>89.88310894580678</v>
+        <v>69.21375185036834</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>74.64007695571522</v>
+        <v>42.92703760172894</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2892930719089598</v>
+        <v>0.4362010178546667</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>41.88671912240289</v>
+        <v>1.399985229669412</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6997</v>
+        <v>6861</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>547.8629076434283</v>
+        <v>620.198033696119</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>351.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>54.14657828685665</v>
+        <v>46.19554139264597</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5.154051301848854</v>
+        <v>46.19878848631676</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.286290764342841</v>
+        <v>0.5198033696118906</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.1633057431040967</v>
+        <v>-19.34540239846555</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, market_above_ma60, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7730</v>
+        <v>6924</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>545.6313771224281</v>
+        <v>618.5488770530234</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>43.16625881643955</v>
+        <v>55.6759714728203</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>26.70391299005051</v>
+        <v>60.22105717827443</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5631377122428231</v>
+        <v>0.854887705302337</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-4.283531777508532</v>
+        <v>-1.577735250980624</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6924</v>
+        <v>7805</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>543.5488770530234</v>
+        <v>616.606489372751</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>157</v>
+        <v>758</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.6759714621931</v>
+        <v>53.93215481211273</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>60.22105715234753</v>
+        <v>37.14499970792571</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.854887705302337</v>
+        <v>0.6606489372750988</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.577735250980624</v>
+        <v>-1.040484001798227</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8039</v>
+        <v>7768</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>539.6390008526753</v>
+        <v>615.6935314082139</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>140.5</v>
+        <v>406.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>47.87827817568167</v>
+        <v>52.85063133397214</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>35.66745755583201</v>
+        <v>20.08816647283959</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.463900085267533</v>
+        <v>0.5693531408213882</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,11 +2849,11 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.352720461035274</v>
+        <v>6.272430737710573</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>538.5692016628188</v>
+        <v>613.5692016628188</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>192.5</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>54.89649838984296</v>
+        <v>54.89649846803731</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>33.38764325163897</v>
+        <v>33.38764314988005</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.3569201662818892</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0734582762475524</v>
+        <v>-0.07345827557979411</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7734</v>
+        <v>7750</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>533.5079305339286</v>
+        <v>612.5733512620069</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>3055</v>
+        <v>2260</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>41.65940529794029</v>
+        <v>46.52071091049724</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>33.73613927000245</v>
+        <v>25.09345226654376</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3507930533928694</v>
+        <v>0.2573351262006949</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-106.5257432757641</v>
+        <v>-61.23937323904973</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7750</v>
+        <v>8021</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>522.573351262007</v>
+        <v>606.4302389989299</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>2260</v>
+        <v>458</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46.5207109110787</v>
+        <v>55.37931827288384</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.09345227067834</v>
+        <v>17.2945531155685</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2573351262006949</v>
+        <v>0.1430238998929903</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-61.23937323952642</v>
+        <v>-0.9255924694848084</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7827</v>
+        <v>8046</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>517.3963139668534</v>
+        <v>603.2288472148354</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>159.5</v>
+        <v>845</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>62.51006248838168</v>
+        <v>49.05182085902324</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>22.1221221245295</v>
+        <v>23.26043432335747</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.239631396685346</v>
+        <v>0.8228847214835364</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>2.955455471254337</v>
+        <v>-8.651015042184323</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8046</v>
+        <v>7769</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>513.2288472148354</v>
+        <v>602.3148150950365</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>845</v>
+        <v>7275</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>49.05182086058509</v>
+        <v>56.08133527200131</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>23.26043443717332</v>
+        <v>39.47539849066999</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8228847214835364</v>
+        <v>0.7314815095036464</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-8.651015043119219</v>
+        <v>-126.6454559390879</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6944</v>
+        <v>6903</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>503.4595588865901</v>
+        <v>600.7899839730266</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>939</v>
+        <v>393</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>54.25269261433137</v>
+        <v>49.03353206622772</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.60935460751934</v>
+        <v>25.09029119853368</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.8459558886590143</v>
+        <v>0.578998397302659</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-1.44738498458856</v>
+        <v>-2.79318428526868</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7828</v>
+        <v>6922</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>499.5669629573283</v>
+        <v>599.6386796249965</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>1565</v>
+        <v>184.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>61.83240033956551</v>
+        <v>48.94346344794253</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>17.15976740424421</v>
+        <v>31.00432408419579</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4566962957328327</v>
+        <v>0.4638679624996468</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>37.83350352494011</v>
+        <v>-1.087150866824745</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7722</v>
+        <v>6951</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>499.2588775641439</v>
+        <v>598.9473119451987</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>305.5</v>
+        <v>82</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>66.37571811342892</v>
+        <v>55.06304631866833</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>27.80502620864054</v>
+        <v>30.52573277649704</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.425887756414388</v>
+        <v>1.894731194519875</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>5.894443353180103</v>
+        <v>0.102310428725568</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8021</v>
+        <v>6944</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>491.4302389989299</v>
+        <v>593.4595588865901</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>458</v>
+        <v>939</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>55.37931827177568</v>
+        <v>54.25269262406579</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.29455318858496</v>
+        <v>14.60935456893146</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1430238998929903</v>
+        <v>0.8459558886590143</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.9255924696183442</v>
+        <v>-1.447384984970126</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6957</v>
+        <v>6901</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>489.8156113150196</v>
+        <v>589.9676059815098</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>191.5</v>
+        <v>14.3</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>76.50662863913121</v>
+        <v>56.86963931934428</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>28.13489034750189</v>
+        <v>17.69164724264987</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.481561131501961</v>
+        <v>0.4967605981509742</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>3.613579743560335</v>
+        <v>0.1651634585033083</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6885</v>
+        <v>6913</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>489.3717723206662</v>
+        <v>583.1364884617898</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>26.55</v>
+        <v>134</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>70.82462707958274</v>
+        <v>48.32396981336196</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.96675037712003</v>
+        <v>20.85923468767889</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>2.437177232066618</v>
+        <v>0.313648846178974</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.543861513235079</v>
+        <v>-1.118264701304264</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7753</v>
+        <v>8048</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>463.1001331672902</v>
+        <v>552.8051655573399</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>43.35</v>
+        <v>63</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.58254535188481</v>
+        <v>51.93329930529098</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>24.18950199056976</v>
+        <v>18.76919492302935</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8100133167290228</v>
+        <v>0.7805165557339908</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0248892567641439</v>
+        <v>0.09147703416481361</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7747</v>
+        <v>7730</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>458.4759189513329</v>
+        <v>545.6313771224281</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>129</v>
+        <v>185</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.01674340283013</v>
+        <v>43.16625882222285</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.9071067943765</v>
+        <v>26.70391300821835</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3475918951332927</v>
+        <v>0.5631377122428231</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2.193668430345045</v>
+        <v>-4.283531777680249</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7749</v>
+        <v>6965</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>455.4058852707356</v>
+        <v>542.7328546669968</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>465</v>
+        <v>81.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45.11610450982754</v>
+        <v>55.31833215215115</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>27.11179412194144</v>
+        <v>26.91671333039229</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5405885270735552</v>
+        <v>0.7732854666996781</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-7.766939732477176</v>
+        <v>0.8429933621120536</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7792</v>
+        <v>8039</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>446.3965558778343</v>
+        <v>539.6390008526753</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>280.5</v>
+        <v>140.5</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>42.96726922195498</v>
+        <v>47.87827816574257</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>22.69456542113806</v>
+        <v>35.66745728143601</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6396555877834276</v>
+        <v>0.463900085267533</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>3.611169765252273</v>
+        <v>-1.352720460548747</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>7768</v>
+        <v>7734</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>445.6935314082139</v>
+        <v>533.5079305339286</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>406.5</v>
+        <v>3055</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.8506313154151</v>
+        <v>41.65940531098265</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.08816644539434</v>
+        <v>33.73613918004366</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5693531408213882</v>
+        <v>0.3507930533928694</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>6.272430737519752</v>
+        <v>-106.5257432654617</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6855</v>
+        <v>7704</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>445.4171929384768</v>
+        <v>513.4565638866869</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>130</v>
+        <v>61.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>58.75665040545777</v>
+        <v>49.79009081573686</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>11.92375162155184</v>
+        <v>17.45647282438101</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.041719293847682</v>
+        <v>0.3456563886686941</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>2.229757946563606</v>
+        <v>-0.6256880947352961</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7732</v>
+        <v>6931</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>431.9506339272235</v>
+        <v>511.0504873187336</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>36.25</v>
+        <v>41.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>58.37378621927243</v>
+        <v>40.44212919496883</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>16.61237309213557</v>
+        <v>44.09714394369886</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.695063392722351</v>
+        <v>0.6050487318733652</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1118231831254704</v>
+        <v>0.4185566651488197</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6877</v>
+        <v>8047</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>424.6093524721673</v>
+        <v>508.1486639202586</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>152</v>
+        <v>50.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.60408182782884</v>
+        <v>53.25380664321511</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19.53193349688235</v>
+        <v>8.207390001632415</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4609352472167276</v>
+        <v>1.314866392025858</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.828913114518498</v>
+        <v>0.9247680892070684</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7795</v>
+        <v>6873</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>418.6859793743408</v>
+        <v>507.8769173311782</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>380</v>
+        <v>93</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46.81123288539244</v>
+        <v>54.57205367811708</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.61000068344661</v>
+        <v>17.89238734484224</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.3685979374340751</v>
+        <v>1.287691733117821</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.796527418424918</v>
+        <v>0.9426988062039756</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6965</v>
+        <v>7803</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>402.7328546669968</v>
+        <v>467.8315226031818</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>81.7</v>
+        <v>23.25</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>55.31833212381399</v>
+        <v>37.41228304817816</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>26.91671303564758</v>
+        <v>24.47525308086334</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.7732854666996781</v>
+        <v>0.7831522603181843</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.8429933608718969</v>
+        <v>-0.0558820798980821</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6994</v>
+        <v>7753</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>384.4982996663251</v>
+        <v>463.1001331672902</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>62.7</v>
+        <v>43.35</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.55357997420426</v>
+        <v>54.58254539578412</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>23.7474308952822</v>
+        <v>24.18950199056976</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.4498299666325149</v>
+        <v>0.8100133167290228</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>1.23356205232841</v>
+        <v>0.0248892567641439</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7704</v>
+        <v>7747</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>373.4565638866869</v>
+        <v>458.4759189513329</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>61.9</v>
+        <v>129</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.79009070441506</v>
+        <v>52.01674340900828</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17.45647283796698</v>
+        <v>11.9071068567868</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3456563886686941</v>
+        <v>0.3475918951332927</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.6256880949070075</v>
+        <v>2.193668430631246</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7717</v>
+        <v>7749</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>368.7670577566946</v>
+        <v>455.4058852707356</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>604</v>
+        <v>465</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>39.49823704749208</v>
+        <v>45.11610450982754</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15.72350909128877</v>
+        <v>27.11179412194144</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8767057756694557</v>
+        <v>0.5405885270735552</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-3.256352898483883</v>
+        <v>-7.766939732477176</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6873</v>
+        <v>7792</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>367.8769173311782</v>
+        <v>446.3965558778343</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>93</v>
+        <v>280.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>54.57205366830809</v>
+        <v>42.96726923969466</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.89238729172534</v>
+        <v>22.69456553115768</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.287691733117821</v>
+        <v>0.6396555877834276</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.9426988058223722</v>
+        <v>3.611169764679936</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8033</v>
+        <v>7821</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>365.6080855751964</v>
+        <v>443.1666902449148</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>134.5</v>
+        <v>45.35</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>43.76232095560122</v>
+        <v>44.55531012883158</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>8.357912940028159</v>
+        <v>24.64035314733669</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5608085575196424</v>
+        <v>0.8166690244914784</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.189852904878168</v>
+        <v>0.7123458100969104</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8048</v>
+        <v>6908</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>362.8051655573399</v>
+        <v>440.1244588296648</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>63</v>
+        <v>40.45</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.93329926980518</v>
+        <v>53.06796400686825</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>18.76919490821635</v>
+        <v>13.08165626785164</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7805165557339908</v>
+        <v>0.5124458829664826</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,11 +4280,11 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.091477034183889</v>
+        <v>0.4867317738938987</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>344.8568148090619</v>
+        <v>434.8568148090619</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>757</v>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.74468067175547</v>
+        <v>51.74468072180979</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10.89967860404625</v>
+        <v>10.89967858658752</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>0.4856814809061923</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>2.704795524448229</v>
+        <v>2.704795523971298</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>7823</v>
+        <v>6918</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>342.1141551682992</v>
+        <v>434.7783787580781</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>44.74400358113698</v>
+        <v>49.16778606377999</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>27.24775372567973</v>
+        <v>10.64357852200988</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.2114155168299255</v>
+        <v>0.4778378758078112</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-1.197815901072328</v>
+        <v>0.0526275404959144</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7803</v>
+        <v>7732</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>327.8315226031818</v>
+        <v>431.9506339272235</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>23.25</v>
+        <v>36.25</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>37.41228301679686</v>
+        <v>58.37378653827422</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>24.47525308327656</v>
+        <v>16.61237308540709</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7831522603181843</v>
+        <v>1.695063392722351</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0558820798885386</v>
+        <v>0.1118231832590226</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6918</v>
+        <v>6877</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>319.7783787580781</v>
+        <v>424.6093524721673</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>74.2</v>
+        <v>152</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.16778608918894</v>
+        <v>44.60408189698399</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>10.64357852200988</v>
+        <v>19.53193345821155</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4778378758078112</v>
+        <v>0.4609352472167276</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0526275403051247</v>
+        <v>-1.828913114232308</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6958</v>
+        <v>7795</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>311.6013069719597</v>
+        <v>418.6859793743408</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>16.9</v>
+        <v>380</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>38.4609527672931</v>
+        <v>46.81123289370684</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.99291374067506</v>
+        <v>15.61000075355447</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6601306971959692</v>
+        <v>0.3685979374340751</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0337397498981572</v>
+        <v>-0.7965274187111087</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8047</v>
+        <v>7780</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>308.1486639202586</v>
+        <v>416.8054971835704</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>50.5</v>
+        <v>18.15</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.25380663391634</v>
+        <v>42.93750996159987</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>8.207390089625729</v>
+        <v>27.04317378437101</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.314866392025858</v>
+        <v>1.180549718357036</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.9247680892261529</v>
+        <v>0.1493380061845144</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6869</v>
+        <v>7822</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>304.4713827577776</v>
+        <v>401.2622231439344</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>83.90000000000001</v>
+        <v>1150</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>48.41201410464964</v>
+        <v>46.52674148413299</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>19.69510853677719</v>
+        <v>18.68578182025222</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.947138275777756</v>
+        <v>1.126222314393439</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.6536980025043194</v>
+        <v>15.42427445826742</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7740</v>
+        <v>6949</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>301.4595573173321</v>
+        <v>394.3569690932899</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>172.5</v>
+        <v>658</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.34094415567061</v>
+        <v>46.23784080581912</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.16903229688987</v>
+        <v>19.57614525673013</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.6459557317332073</v>
+        <v>0.9356969093289896</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.030006836174862</v>
+        <v>-3.046703230802333</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6901</v>
+        <v>7786</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>299.9676059815097</v>
+        <v>394.1511099470368</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>14.3</v>
+        <v>125</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>56.86963925708597</v>
+        <v>51.00101347748252</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.6916471455234</v>
+        <v>19.73183672376693</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4967605981509742</v>
+        <v>1.915110994703684</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.1651634584174511</v>
+        <v>1.07070226162416</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6955</v>
+        <v>6994</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>293.0651380129204</v>
+        <v>384.4982996663251</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>145</v>
+        <v>62.7</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>50.81967848870696</v>
+        <v>51.55358012520059</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>5.507014154034721</v>
+        <v>23.74743095291752</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3065138012920358</v>
+        <v>0.4498299666325149</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>2.515091987690822</v>
+        <v>1.233562052404724</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6931</v>
+        <v>8011</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>281.0504873187336</v>
+        <v>380.753268984088</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>41.3</v>
+        <v>18.9</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>40.4421290793977</v>
+        <v>50.55878496319829</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>44.09714361449404</v>
+        <v>19.3233482122012</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6050487318733652</v>
+        <v>0.5753268984087954</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.4185566652060521</v>
+        <v>0.2055365307035983</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6949</v>
+        <v>6923</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>279.3569690932899</v>
+        <v>370.3002937519918</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>658</v>
+        <v>78.7</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.23784077923892</v>
+        <v>46.17593900087618</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.57614531920317</v>
+        <v>18.17787855241353</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9356969093289896</v>
+        <v>0.5300293751991754</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-3.046703230897755</v>
+        <v>0.132193427421503</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7780</v>
+        <v>7717</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>276.8054971835704</v>
+        <v>368.7670577566946</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>18.15</v>
+        <v>604</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>42.93751065896888</v>
+        <v>39.49823704749208</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>27.04317354454171</v>
+        <v>15.72350909128877</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.180549718357036</v>
+        <v>0.8767057756694557</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.1493380058817464</v>
+        <v>-3.256352898483883</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6933</v>
+        <v>8033</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>275.0178678180006</v>
+        <v>365.6080855751964</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>167.5</v>
+        <v>134.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.82359910997495</v>
+        <v>43.76232094826046</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>14.06074094248677</v>
+        <v>8.357912875845892</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5017867818000664</v>
+        <v>0.5608085575196424</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.7359553128095953</v>
+        <v>-0.1898529043058205</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6863</v>
+        <v>8034</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>261.6696424054682</v>
+        <v>348.1707098762575</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>104</v>
+        <v>24.35</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>43.90785326375853</v>
+        <v>49.55872391679434</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>21.44453798052514</v>
+        <v>12.95897761483086</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6669642405468218</v>
+        <v>1.317070987625753</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-1.12187982661879</v>
+        <v>0.0902493139996748</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7786</v>
+        <v>7631</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>254.1511099470368</v>
+        <v>345.0770356653786</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>125</v>
+        <v>126.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.00101342266103</v>
+        <v>51.90700779028357</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>19.73183657190427</v>
+        <v>14.00879970258206</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.915110994703684</v>
+        <v>0.5077035665378581</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>1.07070226162416</v>
+        <v>-4.557333613837255</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7821</v>
+        <v>7823</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>253.1666902449148</v>
+        <v>342.1141551682992</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>45.35</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.55531025596415</v>
+        <v>44.74400358113698</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>24.64035319788081</v>
+        <v>27.24775372567973</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8166690244914784</v>
+        <v>0.2114155168299255</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.7123458099061111</v>
+        <v>-1.197815901072328</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7715</v>
+        <v>6969</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>249.8190735926242</v>
+        <v>339.7408150692034</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>27.8</v>
+        <v>27.55</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42.54034117476638</v>
+        <v>36.57901992103297</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.08263221430665</v>
+        <v>17.39284683311636</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4819073592624223</v>
+        <v>1.974081506920341</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0810700348604198</v>
+        <v>-0.0010622028134987</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6969</v>
+        <v>6865</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>249.7408150692034</v>
+        <v>334.7751486502656</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>27.55</v>
+        <v>28.95</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>36.57901968842725</v>
+        <v>43.46190508973528</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.39284689123369</v>
+        <v>33.39894964228341</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.974081506920341</v>
+        <v>0.4775148650265652</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0010622027658011</v>
+        <v>0.3343035920931685</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8038</v>
+        <v>6928</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>245.4021433693917</v>
+        <v>333.921464248513</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>41.2</v>
+        <v>46.6</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>47.20383246923522</v>
+        <v>46.07448677648672</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>10.91398997532189</v>
+        <v>16.69292268371252</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.04021433693917</v>
+        <v>0.8921464248512961</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.1571958483820896</v>
+        <v>0.0788767749050362</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6928</v>
+        <v>7402</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>243.921464248513</v>
+        <v>316.3898791901935</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>46.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.07448663452118</v>
+        <v>38.73681430055233</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.69292271649593</v>
+        <v>16.451550372657</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.8921464248512961</v>
+        <v>0.6389879190193565</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0788767748859608</v>
+        <v>0.8758696270296404</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8011</v>
+        <v>6958</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>240.753268984088</v>
+        <v>311.6013069719597</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>18.9</v>
+        <v>16.9</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>50.55878491383839</v>
+        <v>38.46095297743433</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.32334819159237</v>
+        <v>21.99291384616624</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5753268984087954</v>
+        <v>0.6601306971959692</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2055365305986612</v>
+        <v>0.0337397499076957</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7703</v>
+        <v>6869</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>238.1351821877982</v>
+        <v>304.4713827577776</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>200</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>38.85076523299665</v>
+        <v>48.41201409055414</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>9.043165046475297</v>
+        <v>19.69510892175265</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.313518218779819</v>
+        <v>0.947138275777756</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.6477502861416529</v>
+        <v>0.6536980035536822</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6909</v>
+        <v>7740</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>236.6440841079993</v>
+        <v>301.4595573173321</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>48.05</v>
+        <v>172.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>36.9027283241287</v>
+        <v>48.34094412621536</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.8108138864252</v>
+        <v>13.16903229361967</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6644084107999327</v>
+        <v>0.6459557317332073</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.5998794818321058</v>
+        <v>1.030006836938069</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8034</v>
+        <v>6955</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>233.1707098762575</v>
+        <v>293.0651380129204</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>24.35</v>
+        <v>145</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.5587237850883</v>
+        <v>50.81967849877516</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.95897766740738</v>
+        <v>5.507014164064984</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.317070987625753</v>
+        <v>0.3065138012920358</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0902493139805972</v>
+        <v>2.51509198778623</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7822</v>
+        <v>6914</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>231.2622231439344</v>
+        <v>292.9349915590237</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>1150</v>
+        <v>143.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46.52674147414256</v>
+        <v>49.89438271347467</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>18.68578181807824</v>
+        <v>15.44622849947699</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.126222314393439</v>
+        <v>1.293499155902374</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>15.42427445788574</v>
+        <v>0.3141749941739302</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7631</v>
+        <v>7547</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>230.0770356653786</v>
+        <v>286.7367383681788</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>126.5</v>
+        <v>62.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.90700777706413</v>
+        <v>41.15705758409312</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>14.00879970307795</v>
+        <v>19.42334023061793</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5077035665378581</v>
+        <v>0.1736738368178785</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-4.557333613837255</v>
+        <v>-0.3903169272830862</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6919</v>
+        <v>7736</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>227.1668180443034</v>
+        <v>275.6680163256831</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>96</v>
+        <v>72.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.89150756848012</v>
+        <v>43.2267431922088</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.11884023093081</v>
+        <v>21.19286306245663</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.716681804430342</v>
+        <v>1.066801632568311</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.233986574100721</v>
+        <v>0.3806434224033834</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7402</v>
+        <v>6933</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>226.3898791901936</v>
+        <v>275.0178678180006</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>167.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>38.73681423559825</v>
+        <v>48.82359912144085</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.45155043093064</v>
+        <v>14.06074113481495</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.6389879190193565</v>
+        <v>0.5017867818000664</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.8758696268197586</v>
+        <v>0.7359553153853171</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6962</v>
+        <v>6952</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>225.4746318464925</v>
+        <v>265.6809574306924</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>36.05</v>
+        <v>36.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>44.16504362905631</v>
+        <v>42.05923266315585</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.20952501043568</v>
+        <v>19.70675001549954</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5474631846492497</v>
+        <v>0.5680957430692319</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.312705214684304</v>
+        <v>0.0550490732279953</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6937</v>
+        <v>6863</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>220.3249268571631</v>
+        <v>261.6696424054682</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>281.5</v>
+        <v>104</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>41.82026043628453</v>
+        <v>43.90785342091427</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.50243296861678</v>
+        <v>21.4445382169058</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.032492685716314</v>
+        <v>0.6669642405468218</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-3.592905938551749</v>
+        <v>-1.121879825474018</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7751</v>
+        <v>7715</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>217.2928157076391</v>
+        <v>249.8190735926242</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>1545</v>
+        <v>27.8</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>40.55645033064398</v>
+        <v>42.54034108709149</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.44696362858197</v>
+        <v>22.08263226017321</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.729281570763907</v>
+        <v>0.4819073592624223</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-17.3200490322363</v>
+        <v>-0.0810700346982423</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7810</v>
+        <v>8038</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>215.7983509790608</v>
+        <v>245.4021433693917</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>226.5</v>
+        <v>41.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46.55194231372161</v>
+        <v>47.20383246923522</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.74439240250041</v>
+        <v>10.91398999995078</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.5798350979060727</v>
+        <v>1.04021433693917</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2470984829833208</v>
+        <v>0.1571958484297876</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7744</v>
+        <v>7703</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>215.5525032189336</v>
+        <v>238.1351821877982</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>455</v>
+        <v>200</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>37.68599932527567</v>
+        <v>38.85076536785358</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.52064231681009</v>
+        <v>9.043164949062684</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5552503218933621</v>
+        <v>1.313518218779819</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-7.843772651530189</v>
+        <v>-0.6477502860462518</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6854</v>
+        <v>6909</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>214.9935157219282</v>
+        <v>236.6440841079993</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>140</v>
+        <v>48.05</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>40.03544368787263</v>
+        <v>36.90272841742013</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>12.30579156136252</v>
+        <v>13.81081388642519</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4993515721928187</v>
+        <v>0.6644084107999327</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-1.860660278855318</v>
+        <v>-0.5998794816699269</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6983</v>
+        <v>6919</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>213.1313829494713</v>
+        <v>227.1668180443034</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>361</v>
+        <v>96</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.25016035823153</v>
+        <v>42.89150649639384</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15.92436133363146</v>
+        <v>17.11884037495297</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3131382949471248</v>
+        <v>0.716681804430342</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-3.481475863490412</v>
+        <v>-0.2339865642888352</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>7760</v>
+        <v>6962</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>210.2350273929517</v>
+        <v>225.4746318464925</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>32.05</v>
+        <v>36.05</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>28.32647558043608</v>
+        <v>44.16504373119552</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>55.06065615630615</v>
+        <v>14.20952519044038</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.5235027392951734</v>
+        <v>0.5474631846492497</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0034982051063929</v>
+        <v>-0.312705214684304</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7818</v>
+        <v>6937</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>208.7278291102378</v>
+        <v>220.3249268571631</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>64.3</v>
+        <v>281.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>26.09704424833848</v>
+        <v>41.82026039658511</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>41.8439459320764</v>
+        <v>17.5024329006922</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3727829110237851</v>
+        <v>1.032492685716314</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.4943188173700807</v>
+        <v>-3.592905935499036</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6988</v>
+        <v>7751</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>195.048307661945</v>
+        <v>217.2928157076391</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>14.35</v>
+        <v>1545</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>34.75823483999618</v>
+        <v>40.55645033188118</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>25.4600824206358</v>
+        <v>18.44696366379458</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.5048307661945045</v>
+        <v>0.729281570763907</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.2899013133032054</v>
+        <v>-17.32004903204533</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7820</v>
+        <v>7810</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>194.5617444131753</v>
+        <v>215.7983509790608</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>121.5</v>
+        <v>226.5</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>32.54372086234976</v>
+        <v>46.55194233632064</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>26.94492099873716</v>
+        <v>13.74439249382814</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4561744413175281</v>
+        <v>0.5798350979060727</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.3451241400173614</v>
+        <v>-0.2470984828878912</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7842</v>
+        <v>7744</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>194.4921160462725</v>
+        <v>215.5525032189336</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>108.5</v>
+        <v>455</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>37.05893420719071</v>
+        <v>37.68599934112113</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>27.17519111443213</v>
+        <v>18.52064231802137</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4492116046272453</v>
+        <v>0.5552503218933621</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>1.72272280105652</v>
+        <v>-7.843772651339357</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6934</v>
+        <v>6854</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>189.5532521644571</v>
+        <v>214.9935157219282</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>140</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>36.9245623758571</v>
+        <v>40.03544379732542</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>24.39360206469452</v>
+        <v>12.30579147398159</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.455325216445713</v>
+        <v>0.4993515721928187</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1485212126850723</v>
+        <v>-1.860660278187534</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>7736</v>
+        <v>6983</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>185.6680163256831</v>
+        <v>213.1313829494713</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>72.8</v>
+        <v>361</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.2267427075494</v>
+        <v>43.25016035282493</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>21.19286294767817</v>
+        <v>15.92436133481058</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.066801632568311</v>
+        <v>0.3131382949471248</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.3806434219263941</v>
+        <v>-3.481475863108848</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7738</v>
+        <v>7760</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>180.1831780650292</v>
+        <v>210.2350273929517</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>168</v>
+        <v>32.05</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>44.18809523851338</v>
+        <v>28.32647562760417</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>22.91283903663274</v>
+        <v>55.06065610053105</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.5183178065029131</v>
+        <v>0.5235027392951734</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.4429153345085068</v>
+        <v>-0.0034982052208691</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6908</v>
+        <v>7818</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>180.1244588296648</v>
+        <v>208.7278291102378</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>40.45</v>
+        <v>64.3</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>53.06796400686825</v>
+        <v>26.09704418951073</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13.08165626785164</v>
+        <v>41.84394598758656</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5124458829664826</v>
+        <v>0.3727829110237851</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.4867317738938987</v>
+        <v>0.4943188175608703</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6914</v>
+        <v>6887</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>177.9349915590237</v>
+        <v>206.2620343994519</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>143.5</v>
+        <v>34.95</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>49.89438268413635</v>
+        <v>49.43669539732653</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15.44622849211397</v>
+        <v>10.47059733764077</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.293499155902374</v>
+        <v>0.1262034399451916</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.3141749941739302</v>
+        <v>0.7411173825778985</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6952</v>
+        <v>6988</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>175.6809574306923</v>
+        <v>195.048307661945</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>36.5</v>
+        <v>14.35</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>42.05923256336804</v>
+        <v>34.7582353630667</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.70675001549954</v>
+        <v>25.46008257876682</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.5680957430692319</v>
+        <v>0.5048307661945045</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0550490732661528</v>
+        <v>-0.2899013134272222</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7547</v>
+        <v>7820</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>171.7367383681788</v>
+        <v>194.5617444131753</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>62.5</v>
+        <v>121.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>41.15705758074706</v>
+        <v>32.54372086234976</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>19.42334023061792</v>
+        <v>26.94492099873716</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.1736738368178785</v>
+        <v>0.4561744413175281</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.3903169274357247</v>
+        <v>0.3451241400173614</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>8024</v>
+        <v>7842</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>167.4716328131547</v>
+        <v>194.4921160462725</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>12.45</v>
+        <v>108.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>46.7096109947019</v>
+        <v>37.05893420719071</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.9734018504969</v>
+        <v>27.17519111443213</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.7471632813154662</v>
+        <v>0.4492116046272453</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.008402651546304299</v>
+        <v>1.72272280105652</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6923</v>
+        <v>6934</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>165.3002937519918</v>
+        <v>189.5532521644571</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>78.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>46.17593876706498</v>
+        <v>36.92456253932144</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.1778786028767</v>
+        <v>24.39360206960635</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5300293751991754</v>
+        <v>1.455325216445713</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.1321934274596594</v>
+        <v>0.1485212127804507</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7770</v>
+        <v>7738</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>162.8449363424162</v>
+        <v>180.1831780650292</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>43.2</v>
+        <v>168</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>48.69000090684632</v>
+        <v>44.18809524835842</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>7.962532970057519</v>
+        <v>22.9128391376859</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.2844936342416245</v>
+        <v>0.5183178065029131</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.4378047424634596</v>
+        <v>0.4429153347946757</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6921</v>
+        <v>8024</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>161.0345649222204</v>
+        <v>167.4716328131547</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>72.7</v>
+        <v>12.45</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>37.7814184446659</v>
+        <v>46.70961110736491</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>18.70859342648371</v>
+        <v>13.9734018504969</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.103456492222042</v>
+        <v>0.7471632813154662</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.4247245990767685</v>
+        <v>0.008402651594002501</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6967</v>
+        <v>7770</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>157.3980962079417</v>
+        <v>162.8449363424162</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>71.5</v>
+        <v>43.2</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>46.67856919065394</v>
+        <v>48.69000089290824</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>10.86436515373672</v>
+        <v>7.962533046108247</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.7398096207941692</v>
+        <v>0.2844936342416245</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.3025947738714574</v>
+        <v>0.437804742635178</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>6953</v>
+        <v>6921</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>156.6964550302216</v>
+        <v>161.0345649222204</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>237</v>
+        <v>72.7</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>41.02890844965792</v>
+        <v>37.7814184446659</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>15.05993398611652</v>
+        <v>18.70859342648371</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.6696455030221559</v>
+        <v>1.103456492222042</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-2.740327529760745</v>
+        <v>-0.4247245990767685</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6865</v>
+        <v>6967</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>134.7751486502656</v>
+        <v>157.3980962079417</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>28.95</v>
+        <v>71.5</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>43.46190481256505</v>
+        <v>46.67856930323317</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>33.39894957964529</v>
+        <v>10.86436515484612</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.4775148650265652</v>
+        <v>0.7398096207941692</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.3343035920931685</v>
+        <v>-0.3025947740050314</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>8045</v>
+        <v>6953</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>96.50108226581536</v>
+        <v>156.6964550302216</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>65.7</v>
+        <v>237</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>39.52450787759765</v>
+        <v>41.02890840605222</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>16.54980079984155</v>
+        <v>15.05993401004375</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.6501082265815374</v>
+        <v>0.6696455030221559</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.1097177250258685</v>
+        <v>-2.740327528902167</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>6971</v>
+        <v>8045</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>93.64758002710388</v>
+        <v>96.50108226581536</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>27.2</v>
+        <v>65.7</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>41.78657375802511</v>
+        <v>39.52450813245001</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>12.52683534753082</v>
+        <v>16.54980086759187</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.3647580027103886</v>
+        <v>0.6501082265815374</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0620193029218945</v>
+        <v>-0.1097177248159932</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7311,21 +7311,21 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>6887</v>
+        <v>6971</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>91.26203439945192</v>
+        <v>93.64758002710388</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>34.95</v>
+        <v>27.2</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>49.43669531625227</v>
+        <v>41.78657360345596</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>10.47059718816836</v>
+        <v>12.52683536791684</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.1262034399451916</v>
+        <v>0.3647580027103886</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.7411173822726294</v>
+        <v>0.0620193030554507</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
